--- a/data/trans_orig/P21_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P21_R-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado un servicio de urgencias en el último año en 2007</t>
+          <t>Población que ha utilizado un servicio de urgencias en el último año en 2007 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>93187</t>
+          <t>93263</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>132600</t>
+          <t>133358</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>116048</t>
+          <t>115773</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>157168</t>
+          <t>157462</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>223147</t>
+          <t>219861</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>278710</t>
+          <t>277765</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,11%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>561412</t>
+          <t>560654</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>600825</t>
+          <t>600749</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>530242</t>
+          <t>529948</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>571362</t>
+          <t>571637</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1102713</t>
+          <t>1103658</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1158276</t>
+          <t>1161562</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>84,08%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>163278</t>
+          <t>161334</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>211035</t>
+          <t>210904</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>255255</t>
+          <t>252885</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>313033</t>
+          <t>312661</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>435803</t>
+          <t>431448</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>510203</t>
+          <t>508260</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,33%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>750765</t>
+          <t>750896</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>798522</t>
+          <t>800466</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>655360</t>
+          <t>655732</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>713138</t>
+          <t>715508</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,68%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1419990</t>
+          <t>1421933</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1494390</t>
+          <t>1498745</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>77,65%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>103476</t>
+          <t>102352</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>146966</t>
+          <t>144290</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>153553</t>
+          <t>155300</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>199036</t>
+          <t>200494</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>269544</t>
+          <t>267878</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>331745</t>
+          <t>330923</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,29%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>531543</t>
+          <t>534219</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>575033</t>
+          <t>576157</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>484805</t>
+          <t>483347</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>530288</t>
+          <t>528541</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1030605</t>
+          <t>1031427</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1092806</t>
+          <t>1094472</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>80,34%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>115681</t>
+          <t>118074</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>157683</t>
+          <t>158240</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>201841</t>
+          <t>201335</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>256729</t>
+          <t>254588</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>329909</t>
+          <t>331529</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>399614</t>
+          <t>399334</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,17%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>783654</t>
+          <t>783097</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>825656</t>
+          <t>823263</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>781883</t>
+          <t>784024</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>836771</t>
+          <t>837277</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1580335</t>
+          <t>1580615</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1650040</t>
+          <t>1648420</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,26%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>521268</t>
+          <t>515224</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>607385</t>
+          <t>602739</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>774989</t>
+          <t>774864</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>873724</t>
+          <t>872861</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1317955</t>
+          <t>1319432</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1449133</t>
+          <t>1450792</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,8%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2668274</t>
+          <t>2672920</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2754391</t>
+          <t>2760435</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2504533</t>
+          <t>2505396</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2603268</t>
+          <t>2603393</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5204782</t>
+          <t>5203123</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5335960</t>
+          <t>5334483</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>80,17%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado un servicio de urgencias en el último año en 2012</t>
+          <t>Población que ha utilizado un servicio de urgencias en el último año en 2012 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>122231</t>
+          <t>118855</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>161980</t>
+          <t>165202</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>171474</t>
+          <t>170918</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>218544</t>
+          <t>218628</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>303217</t>
+          <t>303521</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>371805</t>
+          <t>365540</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,11%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>540762</t>
+          <t>537540</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>580511</t>
+          <t>583887</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>478506</t>
+          <t>478422</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>525576</t>
+          <t>526132</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1027987</t>
+          <t>1034252</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1096575</t>
+          <t>1096271</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,32%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>201529</t>
+          <t>203032</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>257712</t>
+          <t>257180</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>270992</t>
+          <t>270885</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>328888</t>
+          <t>332494</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>491938</t>
+          <t>485986</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>568994</t>
+          <t>569452</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,78%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>760235</t>
+          <t>760767</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>816418</t>
+          <t>814915</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>703296</t>
+          <t>699690</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>761192</t>
+          <t>761299</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>73,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1481137</t>
+          <t>1480679</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1558193</t>
+          <t>1564145</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>76,29%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>158248</t>
+          <t>159366</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>210807</t>
+          <t>210659</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>231596</t>
+          <t>230720</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>286134</t>
+          <t>284671</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>401115</t>
+          <t>407739</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>476905</t>
+          <t>481704</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,41%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>546816</t>
+          <t>546964</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>599375</t>
+          <t>598257</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>490081</t>
+          <t>491544</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>544619</t>
+          <t>545495</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>70,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1056933</t>
+          <t>1052134</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1132723</t>
+          <t>1126099</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>73,42%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>131188</t>
+          <t>129571</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>175517</t>
+          <t>176328</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>200803</t>
+          <t>201197</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>256452</t>
+          <t>254505</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>346579</t>
+          <t>341940</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>415393</t>
+          <t>416162</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,85%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>770268</t>
+          <t>769457</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>814597</t>
+          <t>816214</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>793302</t>
+          <t>795249</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>848951</t>
+          <t>848557</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1580147</t>
+          <t>1579378</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1648961</t>
+          <t>1653600</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,86%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>658662</t>
+          <t>660984</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>759263</t>
+          <t>758293</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>927222</t>
+          <t>928969</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1038189</t>
+          <t>1042891</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1615706</t>
+          <t>1614116</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1763105</t>
+          <t>1764599</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,28%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2664835</t>
+          <t>2665805</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2765436</t>
+          <t>2763114</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2517014</t>
+          <t>2512312</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2627981</t>
+          <t>2626234</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5216196</t>
+          <t>5214702</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5363595</t>
+          <t>5365185</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>76,87%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado un servicio de urgencias en el último año en 2016</t>
+          <t>Población que ha utilizado un servicio de urgencias en el último año en 2016 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>87454</t>
+          <t>88553</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>125434</t>
+          <t>125839</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>122136</t>
+          <t>121448</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>167583</t>
+          <t>165182</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>221254</t>
+          <t>218136</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>275881</t>
+          <t>279036</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,74%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>547421</t>
+          <t>547016</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>585401</t>
+          <t>584302</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>505256</t>
+          <t>507657</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>550703</t>
+          <t>551391</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1069813</t>
+          <t>1066658</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1124440</t>
+          <t>1127558</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,79%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>152306</t>
+          <t>151911</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>202907</t>
+          <t>203897</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>190904</t>
+          <t>192606</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>245316</t>
+          <t>246972</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>351807</t>
+          <t>358184</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>427814</t>
+          <t>433193</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>21,07%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>813697</t>
+          <t>812707</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>864298</t>
+          <t>864693</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>794228</t>
+          <t>792572</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>848640</t>
+          <t>846938</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1628334</t>
+          <t>1622955</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1704341</t>
+          <t>1697964</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>82,58%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>109112</t>
+          <t>107393</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>151565</t>
+          <t>152219</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>133088</t>
+          <t>134136</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>176745</t>
+          <t>179325</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>250359</t>
+          <t>253605</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>316435</t>
+          <t>316907</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,55%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>607021</t>
+          <t>606367</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>649474</t>
+          <t>651193</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>606995</t>
+          <t>604415</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>650652</t>
+          <t>649604</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1225891</t>
+          <t>1225419</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1291967</t>
+          <t>1288721</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>83,56%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>133704</t>
+          <t>131535</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>181054</t>
+          <t>178197</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>219932</t>
+          <t>223413</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>276319</t>
+          <t>279373</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>367511</t>
+          <t>365484</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>443766</t>
+          <t>439521</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,22%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>754586</t>
+          <t>757443</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>801936</t>
+          <t>804105</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>765641</t>
+          <t>762587</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>822028</t>
+          <t>818547</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1533834</t>
+          <t>1538079</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1610089</t>
+          <t>1612116</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>81,52%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>518647</t>
+          <t>521233</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>608351</t>
+          <t>605503</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>710011</t>
+          <t>714275</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>809947</t>
+          <t>817333</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1257784</t>
+          <t>1256781</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1393367</t>
+          <t>1391939</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,11%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2775333</t>
+          <t>2778181</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2865037</t>
+          <t>2862451</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2728136</t>
+          <t>2720750</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2828072</t>
+          <t>2823808</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5528400</t>
+          <t>5529828</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5663983</t>
+          <t>5664986</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>81,84%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado un servicio de urgencias en el último año en 2023</t>
+          <t>Población que ha utilizado un servicio de urgencias en el último año en 2023 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>108106</t>
+          <t>107730</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>154268</t>
+          <t>151388</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>125069</t>
+          <t>125439</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>161896</t>
+          <t>160903</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>243643</t>
+          <t>247561</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>299053</t>
+          <t>300492</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,95%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>479420</t>
+          <t>482300</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>525582</t>
+          <t>525958</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>513856</t>
+          <t>514849</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>550683</t>
+          <t>550313</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1010388</t>
+          <t>1008949</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1065798</t>
+          <t>1061880</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>81,09%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>117613</t>
+          <t>102201</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>280962</t>
+          <t>278550</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>213853</t>
+          <t>212011</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>262607</t>
+          <t>259144</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>304716</t>
+          <t>286169</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>521869</t>
+          <t>521654</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,27%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>911902</t>
+          <t>914314</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1075251</t>
+          <t>1090663</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>693724</t>
+          <t>697187</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>742478</t>
+          <t>744320</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1627326</t>
+          <t>1627541</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1844479</t>
+          <t>1863026</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>86,68%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>116629</t>
+          <t>117730</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>164157</t>
+          <t>166468</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>227640</t>
+          <t>227968</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>675203</t>
+          <t>643399</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>69,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>358489</t>
+          <t>354914</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>887382</t>
+          <t>865031</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>52,93%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>540523</t>
+          <t>538212</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>588051</t>
+          <t>586950</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>254343</t>
+          <t>286147</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>701906</t>
+          <t>701578</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>746844</t>
+          <t>769195</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1275737</t>
+          <t>1279312</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>47,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>78,28%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>169494</t>
+          <t>171429</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>221425</t>
+          <t>222987</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>222815</t>
+          <t>219548</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>309675</t>
+          <t>308662</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>415137</t>
+          <t>418863</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>513526</t>
+          <t>514994</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,51%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>705406</t>
+          <t>703844</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>757337</t>
+          <t>755402</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>782387</t>
+          <t>783400</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>869247</t>
+          <t>872514</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1505367</t>
+          <t>1503899</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1603756</t>
+          <t>1600030</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>79,25%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>527034</t>
+          <t>524524</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>749197</t>
+          <t>755954</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>871974</t>
+          <t>873901</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1578998</t>
+          <t>1535499</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1504178</t>
+          <t>1526592</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2288957</t>
+          <t>2323565</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,67%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2708867</t>
+          <t>2702110</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2931030</t>
+          <t>2933540</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2074693</t>
+          <t>2118192</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2781717</t>
+          <t>2779790</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4822798</t>
+          <t>4788190</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5607577</t>
+          <t>5585163</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>67,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>78,53%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P21_R-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>93263</t>
+          <t>95197</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>133358</t>
+          <t>132150</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>115773</t>
+          <t>116159</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>157462</t>
+          <t>158133</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>219861</t>
+          <t>221902</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>277765</t>
+          <t>278499</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,16%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>560654</t>
+          <t>561862</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>600749</t>
+          <t>598815</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>529948</t>
+          <t>529277</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>571637</t>
+          <t>571251</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>77,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1103658</t>
+          <t>1102924</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1161562</t>
+          <t>1159521</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>83,94%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>161334</t>
+          <t>162016</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>210904</t>
+          <t>214463</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>252885</t>
+          <t>256145</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>312661</t>
+          <t>313279</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>431448</t>
+          <t>434109</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>508260</t>
+          <t>509971</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,42%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>750896</t>
+          <t>747337</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>800466</t>
+          <t>799784</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>655732</t>
+          <t>655114</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>715508</t>
+          <t>712248</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1421933</t>
+          <t>1420222</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1498745</t>
+          <t>1496084</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>73,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>77,51%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>102352</t>
+          <t>104457</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>144290</t>
+          <t>148278</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>155300</t>
+          <t>156576</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>200494</t>
+          <t>201508</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>267878</t>
+          <t>268060</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>330923</t>
+          <t>327966</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,07%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>534219</t>
+          <t>530231</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>576157</t>
+          <t>574052</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>483347</t>
+          <t>482333</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>528541</t>
+          <t>527265</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1031427</t>
+          <t>1034384</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1094472</t>
+          <t>1094290</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>80,32%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>118074</t>
+          <t>117312</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>158240</t>
+          <t>158891</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>201335</t>
+          <t>201528</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>254588</t>
+          <t>257464</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>331529</t>
+          <t>330930</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>399334</t>
+          <t>403278</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,37%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>783097</t>
+          <t>782446</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>823263</t>
+          <t>824025</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>784024</t>
+          <t>781148</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>837277</t>
+          <t>837084</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1580615</t>
+          <t>1576671</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1648420</t>
+          <t>1649019</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,29%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>515224</t>
+          <t>520496</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>602739</t>
+          <t>605763</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>774864</t>
+          <t>772794</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>872861</t>
+          <t>869588</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1319432</t>
+          <t>1316431</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1450792</t>
+          <t>1454107</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,85%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2672920</t>
+          <t>2669896</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2760435</t>
+          <t>2755163</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2505396</t>
+          <t>2508669</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2603393</t>
+          <t>2605463</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5203123</t>
+          <t>5199808</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5334483</t>
+          <t>5337484</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>80,22%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>118855</t>
+          <t>121641</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>165202</t>
+          <t>164167</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>170918</t>
+          <t>168911</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>218628</t>
+          <t>218959</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>303521</t>
+          <t>301841</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>365540</t>
+          <t>363959</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,0%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>537540</t>
+          <t>538575</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>583887</t>
+          <t>581101</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>478422</t>
+          <t>478091</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>526132</t>
+          <t>528139</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1034252</t>
+          <t>1035833</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1096271</t>
+          <t>1097951</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>78,44%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>203032</t>
+          <t>201486</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>257180</t>
+          <t>256629</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>270885</t>
+          <t>273520</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>332494</t>
+          <t>331841</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>485986</t>
+          <t>491273</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>569452</t>
+          <t>573678</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,98%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>760767</t>
+          <t>761318</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>814915</t>
+          <t>816461</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>699690</t>
+          <t>700343</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>761299</t>
+          <t>758664</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1480679</t>
+          <t>1476453</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1564145</t>
+          <t>1558858</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,04%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>159366</t>
+          <t>160762</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>210659</t>
+          <t>208923</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>230720</t>
+          <t>231863</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>284671</t>
+          <t>286131</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>407739</t>
+          <t>405923</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>481704</t>
+          <t>478923</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,22%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>546964</t>
+          <t>548700</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>598257</t>
+          <t>596861</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>491544</t>
+          <t>490084</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>545495</t>
+          <t>544352</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1052134</t>
+          <t>1054915</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1126099</t>
+          <t>1127915</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>73,54%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>129571</t>
+          <t>128707</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>176328</t>
+          <t>177114</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>201197</t>
+          <t>200287</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>254505</t>
+          <t>254393</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>341940</t>
+          <t>345618</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>416162</t>
+          <t>415761</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,83%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>769457</t>
+          <t>768671</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>816214</t>
+          <t>817078</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>795249</t>
+          <t>795361</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>848557</t>
+          <t>849467</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1579378</t>
+          <t>1579779</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1653600</t>
+          <t>1649922</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>82,68%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>660984</t>
+          <t>653775</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>758293</t>
+          <t>753657</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>928969</t>
+          <t>931378</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1042891</t>
+          <t>1040224</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1614116</t>
+          <t>1617893</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1764599</t>
+          <t>1765029</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,29%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2665805</t>
+          <t>2670441</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2763114</t>
+          <t>2770323</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2512312</t>
+          <t>2514979</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2626234</t>
+          <t>2623825</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5214702</t>
+          <t>5214272</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5365185</t>
+          <t>5361408</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>76,82%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>88553</t>
+          <t>85794</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>125839</t>
+          <t>123904</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>121448</t>
+          <t>120721</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>165182</t>
+          <t>162851</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>218136</t>
+          <t>221807</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>279036</t>
+          <t>277861</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,65%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>547016</t>
+          <t>548951</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>584302</t>
+          <t>587061</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>507657</t>
+          <t>509988</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>551391</t>
+          <t>552118</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1066658</t>
+          <t>1067833</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1127558</t>
+          <t>1123887</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>79,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,52%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>151911</t>
+          <t>150083</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>203897</t>
+          <t>199911</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>192606</t>
+          <t>191441</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>246972</t>
+          <t>245111</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>358184</t>
+          <t>355409</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>433193</t>
+          <t>429668</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,9%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>812707</t>
+          <t>816693</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>864693</t>
+          <t>866521</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>792572</t>
+          <t>794433</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>846938</t>
+          <t>848103</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1622955</t>
+          <t>1626480</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1697964</t>
+          <t>1700739</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,71%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>107393</t>
+          <t>107428</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>152219</t>
+          <t>149420</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>134136</t>
+          <t>131018</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>179325</t>
+          <t>177481</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>253605</t>
+          <t>254234</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>316907</t>
+          <t>316367</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,51%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>606367</t>
+          <t>609166</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>651193</t>
+          <t>651158</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>604415</t>
+          <t>606259</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>649604</t>
+          <t>652722</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1225419</t>
+          <t>1225959</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1288721</t>
+          <t>1288092</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,52%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>131535</t>
+          <t>134013</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>178197</t>
+          <t>179959</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>223413</t>
+          <t>219937</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>279373</t>
+          <t>275519</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>365484</t>
+          <t>369031</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>439521</t>
+          <t>439356</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>757443</t>
+          <t>755681</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>804105</t>
+          <t>801627</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>762587</t>
+          <t>766441</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>818547</t>
+          <t>822023</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1538079</t>
+          <t>1538244</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1612116</t>
+          <t>1608569</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,34%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>521233</t>
+          <t>525366</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>605503</t>
+          <t>610908</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>714275</t>
+          <t>713789</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>817333</t>
+          <t>813841</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1256781</t>
+          <t>1264567</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1391939</t>
+          <t>1399609</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,22%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2778181</t>
+          <t>2772776</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2862451</t>
+          <t>2858318</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2720750</t>
+          <t>2724242</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2823808</t>
+          <t>2824294</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>77,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5529828</t>
+          <t>5522158</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5664986</t>
+          <t>5657200</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>81,73%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>128631</t>
+          <t>138529</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>107730</t>
+          <t>116461</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>151388</t>
+          <t>162657</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>143094</t>
+          <t>153684</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>125439</t>
+          <t>135010</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>160903</t>
+          <t>172120</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>271725</t>
+          <t>292213</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>247561</t>
+          <t>263030</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>300492</t>
+          <t>320289</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,53%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>505057</t>
+          <t>550210</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>482300</t>
+          <t>526082</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>525958</t>
+          <t>572278</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>532658</t>
+          <t>579429</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>514849</t>
+          <t>560993</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>550313</t>
+          <t>598103</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1037716</t>
+          <t>1129639</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1008949</t>
+          <t>1101563</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1061880</t>
+          <t>1158822</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>81,5%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>633688</t>
+          <t>688739</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>633688</t>
+          <t>688739</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>633688</t>
+          <t>688739</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1309441</t>
+          <t>1421852</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1309441</t>
+          <t>1421852</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1309441</t>
+          <t>1421852</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>213681</t>
+          <t>234367</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>102201</t>
+          <t>204203</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>278550</t>
+          <t>265233</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>236136</t>
+          <t>260706</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>212011</t>
+          <t>235967</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>259144</t>
+          <t>288414</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>449817</t>
+          <t>495073</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>286169</t>
+          <t>456678</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>521654</t>
+          <t>540918</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>25,54%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>979183</t>
+          <t>814550</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>914314</t>
+          <t>783684</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1090663</t>
+          <t>844714</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>720195</t>
+          <t>808207</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>697187</t>
+          <t>780499</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>744320</t>
+          <t>832946</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1699378</t>
+          <t>1622757</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1627541</t>
+          <t>1576912</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1863026</t>
+          <t>1661152</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>78,44%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>956331</t>
+          <t>1068913</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>956331</t>
+          <t>1068913</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>956331</t>
+          <t>1068913</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2149195</t>
+          <t>2117830</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2149195</t>
+          <t>2117830</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2149195</t>
+          <t>2117830</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>139569</t>
+          <t>152799</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>117730</t>
+          <t>128610</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>166468</t>
+          <t>181164</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>389764</t>
+          <t>217971</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>227968</t>
+          <t>195210</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>643399</t>
+          <t>241756</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>529333</t>
+          <t>370771</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>354914</t>
+          <t>336807</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>865031</t>
+          <t>407028</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>25,26%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>565111</t>
+          <t>650274</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>538212</t>
+          <t>621909</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>586950</t>
+          <t>674463</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>539782</t>
+          <t>590443</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>286147</t>
+          <t>566658</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>701578</t>
+          <t>613204</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1104893</t>
+          <t>1240716</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>769195</t>
+          <t>1204459</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1279312</t>
+          <t>1274680</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>79,1%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>929546</t>
+          <t>808414</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>929546</t>
+          <t>808414</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>929546</t>
+          <t>808414</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1634226</t>
+          <t>1611487</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1634226</t>
+          <t>1611487</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1634226</t>
+          <t>1611487</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>195043</t>
+          <t>207487</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>171429</t>
+          <t>181328</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>222987</t>
+          <t>236129</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>277492</t>
+          <t>302368</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>219548</t>
+          <t>277971</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>308662</t>
+          <t>329788</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>472536</t>
+          <t>509855</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>418863</t>
+          <t>473607</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>514994</t>
+          <t>548543</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>26,02%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>731788</t>
+          <t>782575</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>703844</t>
+          <t>753933</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>755402</t>
+          <t>808734</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>76,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>814570</t>
+          <t>815358</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>783400</t>
+          <t>787938</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>872514</t>
+          <t>839755</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1546357</t>
+          <t>1597933</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1503899</t>
+          <t>1559245</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1600030</t>
+          <t>1634181</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>73,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>77,53%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1092062</t>
+          <t>1117726</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1092062</t>
+          <t>1117726</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1092062</t>
+          <t>1117726</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2018893</t>
+          <t>2107788</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2018893</t>
+          <t>2107788</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2018893</t>
+          <t>2107788</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>676924</t>
+          <t>733182</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>524524</t>
+          <t>680550</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>755954</t>
+          <t>786603</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1046486</t>
+          <t>934729</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>873901</t>
+          <t>888878</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1535499</t>
+          <t>978948</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1723411</t>
+          <t>1667911</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1526592</t>
+          <t>1598604</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2323565</t>
+          <t>1743154</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>24,01%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2781140</t>
+          <t>2797610</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2702110</t>
+          <t>2744189</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2933540</t>
+          <t>2850242</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2607205</t>
+          <t>2793437</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2118192</t>
+          <t>2749218</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2779790</t>
+          <t>2839288</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>5388344</t>
+          <t>5591047</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4788190</t>
+          <t>5515804</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5585163</t>
+          <t>5660354</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>77,98%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3458064</t>
+          <t>3530792</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3458064</t>
+          <t>3530792</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3458064</t>
+          <t>3530792</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3653691</t>
+          <t>3728166</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3653691</t>
+          <t>3728166</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3653691</t>
+          <t>3728166</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7111755</t>
+          <t>7258958</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7111755</t>
+          <t>7258958</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7111755</t>
+          <t>7258958</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
